--- a/public/data/Base_CeNtro Partner.xlsx
+++ b/public/data/Base_CeNtro Partner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CeNtro Partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{116830F0-27A5-4027-8928-ACFFC964DB35}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B41ABCCE-996D-480D-854C-83B4D1492F3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
   </bookViews>
@@ -710,7 +710,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -780,47 +780,32 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -898,38 +883,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="6"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1271,7 +1224,227 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1399,102 +1572,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2671,128 +2748,36 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="6"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -2810,7 +2795,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:E19" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:E19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
   <autoFilter ref="A1:E19" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E19">
     <sortCondition ref="A2:A19" customList="Partner,Cliente,Negocio"/>
@@ -2827,63 +2812,63 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8C5E01EB-7341-4843-915C-8257323248EA}" name="Desempeño" displayName="Desempeño" ref="A1:H73" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8C5E01EB-7341-4843-915C-8257323248EA}" name="Desempeño" displayName="Desempeño" ref="A1:H73" dataDxfId="86">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{78AD0C5E-A8AA-4CB3-9168-E0107531279B}" name="CeCo" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{75AC09E7-B3E2-4E40-8A4C-B26E4D39223A}" name="ene" dataDxfId="77" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{7E78693C-A6A2-4AF3-9193-850E3285B095}" name="feb" dataDxfId="76" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{9B2459EF-EF12-44AE-8E56-7C0B7BFE3858}" name="mar" dataDxfId="75" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{8882EEB9-4FFD-4D23-96E1-073C5DD693F1}" name="abr" dataDxfId="74" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{D5CF8872-BAE8-4C0C-9493-2F30EFA10DBD}" name="may" dataDxfId="73" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{9E15206F-3384-46EB-AD0D-E866369B8131}" name="jun" dataDxfId="72" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{2201D65E-28DD-4748-8399-A4DCBFF2D8A0}" name="YTD" dataDxfId="71" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{78AD0C5E-A8AA-4CB3-9168-E0107531279B}" name="CeCo" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{75AC09E7-B3E2-4E40-8A4C-B26E4D39223A}" name="ene" dataDxfId="84" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{7E78693C-A6A2-4AF3-9193-850E3285B095}" name="feb" dataDxfId="83" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{9B2459EF-EF12-44AE-8E56-7C0B7BFE3858}" name="mar" dataDxfId="82" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{8882EEB9-4FFD-4D23-96E1-073C5DD693F1}" name="abr" dataDxfId="81" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{D5CF8872-BAE8-4C0C-9493-2F30EFA10DBD}" name="may" dataDxfId="80" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{9E15206F-3384-46EB-AD0D-E866369B8131}" name="jun" dataDxfId="79" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{2201D65E-28DD-4748-8399-A4DCBFF2D8A0}" name="YTD" dataDxfId="78" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1F78B71A-1B12-4FB8-AEC0-1B482898E867}" name="Bebida" displayName="Bebida" ref="A1:H73" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1F78B71A-1B12-4FB8-AEC0-1B482898E867}" name="Bebida" displayName="Bebida" ref="A1:H73" dataDxfId="77">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AC74C680-FF83-44A5-A570-52AEBB5DE765}" name="CeCo" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{B95A0533-232D-49B3-80FD-1E659CCB461D}" name="ene" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{4FA9D1B5-12A8-4604-8E31-1378410B4116}" name="feb" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{C949D5DD-B656-4873-AF48-B68220849179}" name="mar" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{0A2BFEA0-7182-4189-B5A7-4FF7AE19A1E3}" name="abr" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{76178BA1-A6FA-4D82-8AFC-D61625038618}" name="may" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{6D8EBE12-BAA6-40B3-9838-8EC0E1D854C0}" name="jun" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{4D6F7AE1-0A4A-4B7D-AD57-EF11C94ED7A7}" name="YTD" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{AC74C680-FF83-44A5-A570-52AEBB5DE765}" name="CeCo" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{B95A0533-232D-49B3-80FD-1E659CCB461D}" name="ene" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{4FA9D1B5-12A8-4604-8E31-1378410B4116}" name="feb" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{C949D5DD-B656-4873-AF48-B68220849179}" name="mar" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{0A2BFEA0-7182-4189-B5A7-4FF7AE19A1E3}" name="abr" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{76178BA1-A6FA-4D82-8AFC-D61625038618}" name="may" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{6D8EBE12-BAA6-40B3-9838-8EC0E1D854C0}" name="jun" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{4D6F7AE1-0A4A-4B7D-AD57-EF11C94ED7A7}" name="YTD" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FCF9DF4-5C3E-4DA1-B316-5C45F03679A8}" name="Bebida2" displayName="Bebida2" ref="A1:H73" dataDxfId="148">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4FCF9DF4-5C3E-4DA1-B316-5C45F03679A8}" name="Bebida2" displayName="Bebida2" ref="A1:H73" dataDxfId="68">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{BDEC9A2D-F1CB-4191-9A5D-36C157D93B0B}" name="CeCo" dataDxfId="147"/>
-    <tableColumn id="2" xr3:uid="{60D76EA5-57FF-45FB-8457-186785B1E3BC}" name="ene" dataDxfId="146"/>
-    <tableColumn id="3" xr3:uid="{C71CA7B2-ABF3-40D4-8192-DC7E123D2024}" name="feb" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{25F55129-E719-4554-8B64-34CF1D2C669A}" name="mar" dataDxfId="144"/>
-    <tableColumn id="5" xr3:uid="{9B00C926-C150-4C7D-A666-99050F80A8C7}" name="abr" dataDxfId="143"/>
-    <tableColumn id="6" xr3:uid="{D5E4AF0B-39C6-4E12-A4D4-6FCD08001F08}" name="may" dataDxfId="142"/>
-    <tableColumn id="7" xr3:uid="{3618A33C-2533-412F-BC18-6FEB1B9D951D}" name="jun" dataDxfId="141"/>
-    <tableColumn id="8" xr3:uid="{33E35878-7C9B-492D-86FB-31E15D25076E}" name="YTD" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{BDEC9A2D-F1CB-4191-9A5D-36C157D93B0B}" name="CeCo" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{60D76EA5-57FF-45FB-8457-186785B1E3BC}" name="ene" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{C71CA7B2-ABF3-40D4-8192-DC7E123D2024}" name="feb" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{25F55129-E719-4554-8B64-34CF1D2C669A}" name="mar" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{9B00C926-C150-4C7D-A666-99050F80A8C7}" name="abr" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{D5E4AF0B-39C6-4E12-A4D4-6FCD08001F08}" name="may" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{3618A33C-2533-412F-BC18-6FEB1B9D951D}" name="jun" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{33E35878-7C9B-492D-86FB-31E15D25076E}" name="YTD" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C0EE0A4-4E0D-44E4-A543-91ADD208B26D}" name="Bebida29" displayName="Bebida29" ref="A1:G73" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C0EE0A4-4E0D-44E4-A543-91ADD208B26D}" name="Bebida29" displayName="Bebida29" ref="A1:G73" dataDxfId="59">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B00A6E64-852B-457F-871E-16D0189CDAFB}" name="CeCo" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{E8125C17-9F5F-4C77-8778-C315ECA3BCF6}" name="ene" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{D83DDB2A-976E-4992-8EA5-EF739A3A9A8F}" name="feb" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{3D4BD94F-4ACC-4AE3-A2EF-E27C4B140514}" name="mar" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{60FFDEC4-C645-43DA-A8B8-C573CD6FFA42}" name="abr" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{B87EC187-4AEE-4E3D-8821-FA4796111801}" name="may" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{23BF3F0C-F58B-4688-9370-32CC2F18FA77}" name="jun" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{B00A6E64-852B-457F-871E-16D0189CDAFB}" name="CeCo" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{E8125C17-9F5F-4C77-8778-C315ECA3BCF6}" name="ene" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{D83DDB2A-976E-4992-8EA5-EF739A3A9A8F}" name="feb" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{3D4BD94F-4ACC-4AE3-A2EF-E27C4B140514}" name="mar" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{60FFDEC4-C645-43DA-A8B8-C573CD6FFA42}" name="abr" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{B87EC187-4AEE-4E3D-8821-FA4796111801}" name="may" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{23BF3F0C-F58B-4688-9370-32CC2F18FA77}" name="jun" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2906,87 +2891,87 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}" name="Estabilidad12M" displayName="Estabilidad12M" ref="A1:G73" headerRowDxfId="36" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}" name="Estabilidad12M" displayName="Estabilidad12M" ref="A1:G73" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8760413A-3DC9-42CF-B4EA-5B5F6E1D9F88}" name="CeCo" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{FD45D0C1-DDDA-4184-B66F-175777AB3E65}" name="ene" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{D2D9EF56-FC3C-407E-B0EE-5525FD2E795B}" name="feb" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{654B09EF-4021-4323-ABAF-B2700F308F33}" name="mar" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{4662FD58-A3D3-406A-BE18-0921110C19A3}" name="abr" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{07656C8D-75E7-44F8-9FEB-C2D1985DD68D}" name="may" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{6C06EEED-C57C-46DE-AB7B-9E9CADAD0F08}" name="jun" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{8760413A-3DC9-42CF-B4EA-5B5F6E1D9F88}" name="CeCo" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{FD45D0C1-DDDA-4184-B66F-175777AB3E65}" name="ene" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{D2D9EF56-FC3C-407E-B0EE-5525FD2E795B}" name="feb" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{654B09EF-4021-4323-ABAF-B2700F308F33}" name="mar" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{4662FD58-A3D3-406A-BE18-0921110C19A3}" name="abr" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{07656C8D-75E7-44F8-9FEB-C2D1985DD68D}" name="may" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{6C06EEED-C57C-46DE-AB7B-9E9CADAD0F08}" name="jun" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7B08D3E-9BCB-4339-A04A-AD050E056D06}" name="Estabilidad12M18" displayName="Estabilidad12M18" ref="A1:G73" headerRowDxfId="37" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7B08D3E-9BCB-4339-A04A-AD050E056D06}" name="Estabilidad12M18" displayName="Estabilidad12M18" ref="A1:G73" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{19B9A2B4-B3D4-44C9-8157-445235E3EEB4}" name="CeCo" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{B1754C82-3B06-4F4F-B512-C855F9CA0A28}" name="ene" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{83379F9C-FAFC-44E2-8B8A-EB49A62B1560}" name="feb" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{C93E3DBE-BD63-4501-960F-EC81078273C5}" name="mar" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{1AEE55EF-1486-4269-AD44-5FCA47F0CA5C}" name="abr" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{E1106030-ECD7-437C-AAD8-98A694A6AFF2}" name="may" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{72B0E4C3-BFAF-4AFC-865A-DA1CBCD78992}" name="jun" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{19B9A2B4-B3D4-44C9-8157-445235E3EEB4}" name="CeCo" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{B1754C82-3B06-4F4F-B512-C855F9CA0A28}" name="ene" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{83379F9C-FAFC-44E2-8B8A-EB49A62B1560}" name="feb" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{C93E3DBE-BD63-4501-960F-EC81078273C5}" name="mar" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{1AEE55EF-1486-4269-AD44-5FCA47F0CA5C}" name="abr" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{E1106030-ECD7-437C-AAD8-98A694A6AFF2}" name="may" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{72B0E4C3-BFAF-4AFC-865A-DA1CBCD78992}" name="jun" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}" name="Barista" displayName="Barista" ref="A1:G73" headerRowDxfId="35" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}" name="Barista" displayName="Barista" ref="A1:G73" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:G73" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{7B2B1482-8663-4FFB-8A57-866893B5A61D}" name="CeCo" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{4086DE32-21D4-4E6C-93AB-1F974A9FFBB3}" name="ene" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{E2BB6C81-BE61-4C13-8DE7-683971F67A00}" name="feb" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{B0E78386-D205-4857-A8E3-8F28ECF28F52}" name="mar" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{F809E696-69B4-463B-81DC-21EC1196C761}" name="abr" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{ABFC3013-5DE5-4AF9-BFCB-45FF33E0AC07}" name="may" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{F0E01388-AE42-47AC-87ED-9646838B2E51}" name="jun" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{7B2B1482-8663-4FFB-8A57-866893B5A61D}" name="CeCo" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{4086DE32-21D4-4E6C-93AB-1F974A9FFBB3}" name="ene" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E2BB6C81-BE61-4C13-8DE7-683971F67A00}" name="feb" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{B0E78386-D205-4857-A8E3-8F28ECF28F52}" name="mar" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{F809E696-69B4-463B-81DC-21EC1196C761}" name="abr" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{ABFC3013-5DE5-4AF9-BFCB-45FF33E0AC07}" name="may" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{F0E01388-AE42-47AC-87ED-9646838B2E51}" name="jun" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}" name="Supervisor" displayName="Supervisor" ref="A1:G73" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}" name="Supervisor" displayName="Supervisor" ref="A1:G73" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:G73" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A39D1530-373E-49AC-98C3-67FBDCF66ADF}" name="CeCo" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{05AB85B8-7EE2-4F46-BCB0-D8745A79A727}" name="ene" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{8D184D13-D90E-4C36-927A-4D7F59450943}" name="feb" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{9C9A7828-F85C-41AA-AE6B-C928C791F723}" name="mar" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{858F5C44-74CD-4DDC-B14A-C3C05D1A1230}" name="abr" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{FBE60864-83AB-4532-8B8A-0DE740421BF5}" name="may" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{242FC6BB-64AE-4764-AFEB-2281526B13C4}" name="jun" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{A39D1530-373E-49AC-98C3-67FBDCF66ADF}" name="CeCo" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{05AB85B8-7EE2-4F46-BCB0-D8745A79A727}" name="ene" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{8D184D13-D90E-4C36-927A-4D7F59450943}" name="feb" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9C9A7828-F85C-41AA-AE6B-C928C791F723}" name="mar" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{858F5C44-74CD-4DDC-B14A-C3C05D1A1230}" name="abr" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{FBE60864-83AB-4532-8B8A-0DE740421BF5}" name="may" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{242FC6BB-64AE-4764-AFEB-2281526B13C4}" name="jun" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:G73" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}" name="ADTAA" displayName="ADTAA" ref="A1:H69" totalsRowShown="0" headerRowDxfId="139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}" name="ADTAA" displayName="ADTAA" ref="A1:H69" totalsRowShown="0" headerRowDxfId="146">
   <autoFilter ref="A1:H69" xr:uid="{01DC7C7D-B880-4240-925D-62B0CE50CB09}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8FDFBC9A-DC43-478C-9F21-55F0588F95B6}" name="CeCo"/>
@@ -3003,85 +2988,85 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}" name="Tabla3" displayName="Tabla3" ref="A1:H73" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137" tableBorderDxfId="136" dataCellStyle="Porcentaje">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}" name="Tabla3" displayName="Tabla3" ref="A1:H73" totalsRowShown="0" headerRowDxfId="145" dataDxfId="144" tableBorderDxfId="143" dataCellStyle="Porcentaje">
   <autoFilter ref="A1:H73" xr:uid="{D0C7097E-5E75-45DB-BB3B-3108D178A69C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C2EFC2B4-3432-4F83-8EA1-D7172138AB9B}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{DD1CCE8C-1F33-4D7E-8B7D-850C5836F03D}" name="ene" dataDxfId="135" dataCellStyle="Porcentaje"/>
-    <tableColumn id="3" xr3:uid="{5F81742B-8ACA-4CAA-9BC4-A7EDCFD7AF34}" name="feb" dataDxfId="134" dataCellStyle="Porcentaje"/>
-    <tableColumn id="4" xr3:uid="{CCF6FCAC-A5BC-4B9E-9076-999AC278D7B6}" name="mar" dataDxfId="133" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{54ABFB2E-13EA-427F-91FB-47E666195CF6}" name="abr" dataDxfId="132" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{22800C96-3B11-4883-80D9-26FEA549F2EF}" name="may" dataDxfId="131" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{9AE01694-9EB4-4C3E-8091-31272AA10FAC}" name="jun" dataDxfId="130" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{9AEE286D-E013-445D-8F31-2EDBF809F4EE}" name="YTD" dataDxfId="129" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{DD1CCE8C-1F33-4D7E-8B7D-850C5836F03D}" name="ene" dataDxfId="142" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{5F81742B-8ACA-4CAA-9BC4-A7EDCFD7AF34}" name="feb" dataDxfId="141" dataCellStyle="Porcentaje"/>
+    <tableColumn id="4" xr3:uid="{CCF6FCAC-A5BC-4B9E-9076-999AC278D7B6}" name="mar" dataDxfId="140" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{54ABFB2E-13EA-427F-91FB-47E666195CF6}" name="abr" dataDxfId="139" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{22800C96-3B11-4883-80D9-26FEA549F2EF}" name="may" dataDxfId="138" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{9AE01694-9EB4-4C3E-8091-31272AA10FAC}" name="jun" dataDxfId="137" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{9AEE286D-E013-445D-8F31-2EDBF809F4EE}" name="YTD" dataDxfId="136" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}" name="vsppto" displayName="vsppto" ref="A1:H73" totalsRowShown="0" headerRowDxfId="128" tableBorderDxfId="127">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}" name="vsppto" displayName="vsppto" ref="A1:H73" totalsRowShown="0" headerRowDxfId="135" tableBorderDxfId="134">
   <autoFilter ref="A1:H73" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1B86AC11-BA6E-4409-9BCC-D0BFC1CD56F4}" name="CeCo" dataDxfId="126"/>
-    <tableColumn id="2" xr3:uid="{0F192631-4FFF-4FD5-A95D-3C108F8BE19E}" name="ene" dataDxfId="125"/>
-    <tableColumn id="3" xr3:uid="{6C8B16E6-4F77-41EA-8B61-4534855E870F}" name="feb" dataDxfId="124"/>
-    <tableColumn id="4" xr3:uid="{94D35D35-5DDF-4D12-805B-731F38DE0744}" name="mar" dataDxfId="123"/>
-    <tableColumn id="5" xr3:uid="{3440F7B1-3F7A-4549-9C3E-B7C6B54E89C3}" name="abr" dataDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{6FEDA900-B0EC-4A56-A276-007F8F32C55D}" name="may" dataDxfId="121"/>
-    <tableColumn id="7" xr3:uid="{81D19149-D98D-4166-BE81-99492658343E}" name="jun" dataDxfId="120"/>
-    <tableColumn id="9" xr3:uid="{FC882C39-EC0B-4DDB-AA25-5A67064B8F8F}" name="YTD" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{1B86AC11-BA6E-4409-9BCC-D0BFC1CD56F4}" name="CeCo" dataDxfId="133"/>
+    <tableColumn id="2" xr3:uid="{0F192631-4FFF-4FD5-A95D-3C108F8BE19E}" name="ene" dataDxfId="132"/>
+    <tableColumn id="3" xr3:uid="{6C8B16E6-4F77-41EA-8B61-4534855E870F}" name="feb" dataDxfId="131"/>
+    <tableColumn id="4" xr3:uid="{94D35D35-5DDF-4D12-805B-731F38DE0744}" name="mar" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{3440F7B1-3F7A-4549-9C3E-B7C6B54E89C3}" name="abr" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{6FEDA900-B0EC-4A56-A276-007F8F32C55D}" name="may" dataDxfId="128"/>
+    <tableColumn id="7" xr3:uid="{81D19149-D98D-4166-BE81-99492658343E}" name="jun" dataDxfId="127"/>
+    <tableColumn id="9" xr3:uid="{FC882C39-EC0B-4DDB-AA25-5A67064B8F8F}" name="YTD" dataDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{785FD011-3A39-431D-A263-BADB6BDE3D94}" name="ATAA" displayName="ATAA" ref="A1:H73" totalsRowShown="0" headerRowDxfId="118" tableBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{785FD011-3A39-431D-A263-BADB6BDE3D94}" name="ATAA" displayName="ATAA" ref="A1:H73" totalsRowShown="0" headerRowDxfId="125" tableBorderDxfId="124">
   <autoFilter ref="A1:H73" xr:uid="{AF4AFD2D-F1F3-4FAB-BCF9-9DC13F7DF0DB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{59F38E1E-38B2-46EB-AA01-ADB6B981128B}" name="CeCo" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{649F4E8B-772D-4A07-883A-297BE711DD85}" name="ene" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{66FA2D07-7D7A-4218-A261-1BD7FC710740}" name="feb" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{211538EC-1884-443F-8454-BA77B7F28EB8}" name="mar" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{5FAA8758-FD12-4BE9-8965-A65E5A65313A}" name="abr" dataDxfId="112"/>
-    <tableColumn id="6" xr3:uid="{7A0AFBD2-AD5B-4447-9BE2-1EFC4F9F14E6}" name="may" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{2E6A7F3C-986D-45C2-8461-88E38A95D878}" name="jun" dataDxfId="110"/>
-    <tableColumn id="9" xr3:uid="{C4817951-A012-4EB9-A097-61BDB11840CF}" name="YTD" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{59F38E1E-38B2-46EB-AA01-ADB6B981128B}" name="CeCo" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{649F4E8B-772D-4A07-883A-297BE711DD85}" name="ene" dataDxfId="122"/>
+    <tableColumn id="3" xr3:uid="{66FA2D07-7D7A-4218-A261-1BD7FC710740}" name="feb" dataDxfId="121"/>
+    <tableColumn id="4" xr3:uid="{211538EC-1884-443F-8454-BA77B7F28EB8}" name="mar" dataDxfId="120"/>
+    <tableColumn id="5" xr3:uid="{5FAA8758-FD12-4BE9-8965-A65E5A65313A}" name="abr" dataDxfId="119"/>
+    <tableColumn id="6" xr3:uid="{7A0AFBD2-AD5B-4447-9BE2-1EFC4F9F14E6}" name="may" dataDxfId="118"/>
+    <tableColumn id="7" xr3:uid="{2E6A7F3C-986D-45C2-8461-88E38A95D878}" name="jun" dataDxfId="117"/>
+    <tableColumn id="9" xr3:uid="{C4817951-A012-4EB9-A097-61BDB11840CF}" name="YTD" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}" name="COGs" displayName="COGs" ref="A1:H73" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" tableBorderDxfId="106" dataCellStyle="Porcentaje">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}" name="COGs" displayName="COGs" ref="A1:H73" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114" tableBorderDxfId="113" dataCellStyle="Porcentaje">
   <autoFilter ref="A1:H73" xr:uid="{2DD3D2A3-A6E2-4CB5-9D8E-24B27DF07237}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{667DC932-8C9B-46B6-B69B-96B71DAF4178}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{25813112-0CE9-407E-96F8-B767A9AE96A5}" name="ene" dataDxfId="105" dataCellStyle="Porcentaje"/>
-    <tableColumn id="3" xr3:uid="{E3C2F824-C740-4FC7-9642-451285CB6F5D}" name="feb" dataDxfId="104" dataCellStyle="Porcentaje"/>
-    <tableColumn id="4" xr3:uid="{7DBF1ADB-188E-4719-B609-90E4FAE2B065}" name="mar" dataDxfId="103" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{64D0EC7E-5580-47D9-9282-8484D3456183}" name="abr" dataDxfId="102" dataCellStyle="Porcentaje"/>
-    <tableColumn id="6" xr3:uid="{D79D7ABE-ED71-4183-A66E-79E1CC6B60FA}" name="may" dataDxfId="101" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{17FCC6E9-A5AD-4020-A99D-814FE44E7F5D}" name="jun" dataDxfId="100" dataCellStyle="Porcentaje"/>
-    <tableColumn id="8" xr3:uid="{3222E955-FFE4-46F7-B236-F5CA3C55ED76}" name="YTD" dataDxfId="99" dataCellStyle="Porcentaje"/>
+    <tableColumn id="2" xr3:uid="{25813112-0CE9-407E-96F8-B767A9AE96A5}" name="ene" dataDxfId="112" dataCellStyle="Porcentaje"/>
+    <tableColumn id="3" xr3:uid="{E3C2F824-C740-4FC7-9642-451285CB6F5D}" name="feb" dataDxfId="111" dataCellStyle="Porcentaje"/>
+    <tableColumn id="4" xr3:uid="{7DBF1ADB-188E-4719-B609-90E4FAE2B065}" name="mar" dataDxfId="110" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{64D0EC7E-5580-47D9-9282-8484D3456183}" name="abr" dataDxfId="109" dataCellStyle="Porcentaje"/>
+    <tableColumn id="6" xr3:uid="{D79D7ABE-ED71-4183-A66E-79E1CC6B60FA}" name="may" dataDxfId="108" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{17FCC6E9-A5AD-4020-A99D-814FE44E7F5D}" name="jun" dataDxfId="107" dataCellStyle="Porcentaje"/>
+    <tableColumn id="8" xr3:uid="{3222E955-FFE4-46F7-B236-F5CA3C55ED76}" name="YTD" dataDxfId="106" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}" name="Tabla7" displayName="Tabla7" ref="A1:H73" totalsRowShown="0" headerRowDxfId="98" dataDxfId="97" tableBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}" name="Tabla7" displayName="Tabla7" ref="A1:H73" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104" tableBorderDxfId="103">
   <autoFilter ref="A1:H73" xr:uid="{26E4F941-1AF1-4001-AEDB-7D7F50D6DF3C}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{45603471-A800-4D4D-B27B-793376C68BE7}" name="CeCo"/>
-    <tableColumn id="2" xr3:uid="{FF41D456-26E8-4A96-85C1-0DE38E3AB2F8}" name="ene" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{554B0815-E0AE-45F8-926D-06F26DE3B057}" name="feb" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{736CBF7F-B990-42E7-B15E-5B0C67E537EE}" name="mar" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{A234C2C3-97E3-4872-A2DE-111C792DC591}" name="abr" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{791C4ED2-A9F3-4442-900E-D66577C955BF}" name="may" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{696D958C-1D64-4C51-AE13-F3BBC6A497F1}" name="jun" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{8D86F959-E75E-48A9-B708-E9580836BAB6}" name="YTD" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{FF41D456-26E8-4A96-85C1-0DE38E3AB2F8}" name="ene" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{554B0815-E0AE-45F8-926D-06F26DE3B057}" name="feb" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{736CBF7F-B990-42E7-B15E-5B0C67E537EE}" name="mar" dataDxfId="100"/>
+    <tableColumn id="5" xr3:uid="{A234C2C3-97E3-4872-A2DE-111C792DC591}" name="abr" dataDxfId="99"/>
+    <tableColumn id="6" xr3:uid="{791C4ED2-A9F3-4442-900E-D66577C955BF}" name="may" dataDxfId="98"/>
+    <tableColumn id="7" xr3:uid="{696D958C-1D64-4C51-AE13-F3BBC6A497F1}" name="jun" dataDxfId="97"/>
+    <tableColumn id="8" xr3:uid="{8D86F959-E75E-48A9-B708-E9580836BAB6}" name="YTD" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3104,16 +3089,16 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FF52C812-65CA-4F77-A20D-9577DD80438C}" name="Conexion" displayName="Conexion" ref="A1:H73" dataDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FF52C812-65CA-4F77-A20D-9577DD80438C}" name="Conexion" displayName="Conexion" ref="A1:H73" dataDxfId="95">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CBEFF17C-36D0-4285-B054-C2717E2F836E}" name="CeCo" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{723CF5E2-1296-4829-B678-30B9F1C59839}" name="ene" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{AEF08694-1B5C-472F-9138-C35C6046EF1E}" name="feb" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{C8B61DB1-6698-4C99-8019-D7366922E31C}" name="mar" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{AA297A15-CBAC-4D29-8354-6E845D1FE939}" name="abr" dataDxfId="83"/>
-    <tableColumn id="6" xr3:uid="{EADFFD7F-EF42-42E2-889B-295973B77A72}" name="may" dataDxfId="82"/>
-    <tableColumn id="7" xr3:uid="{955A7129-B6F6-47A2-AD6F-CA12B3E0592A}" name="jun" dataDxfId="81"/>
-    <tableColumn id="8" xr3:uid="{554452BD-6543-4D8C-88F4-78E82C298799}" name="YTD" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{CBEFF17C-36D0-4285-B054-C2717E2F836E}" name="CeCo" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{723CF5E2-1296-4829-B678-30B9F1C59839}" name="ene" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{AEF08694-1B5C-472F-9138-C35C6046EF1E}" name="feb" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{C8B61DB1-6698-4C99-8019-D7366922E31C}" name="mar" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{AA297A15-CBAC-4D29-8354-6E845D1FE939}" name="abr" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{EADFFD7F-EF42-42E2-889B-295973B77A72}" name="may" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{955A7129-B6F6-47A2-AD6F-CA12B3E0592A}" name="jun" dataDxfId="88"/>
+    <tableColumn id="8" xr3:uid="{554452BD-6543-4D8C-88F4-78E82C298799}" name="YTD" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3448,47 +3433,47 @@
     <col min="13" max="13" width="8.6328125" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="29" customHeight="1">
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="41" t="s">
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="41" t="s">
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="44" t="s">
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="40" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="46"/>
-      <c r="C2" s="45"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="29" t="s">
         <v>109</v>
       </c>
@@ -3543,21 +3528,21 @@
       <c r="U2" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="V2" s="44"/>
+      <c r="V2" s="40"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="V3" s="47">
+      <c r="V3" s="35">
         <v>0.88</v>
       </c>
     </row>
     <row r="4" spans="2:22">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="36" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -3565,7 +3550,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="36" t="s">
         <v>13</v>
       </c>
       <c r="C5">
@@ -3573,7 +3558,7 @@
       </c>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="36" t="s">
         <v>14</v>
       </c>
       <c r="C6">
@@ -3582,12 +3567,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23514,7 +23499,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="32" t="s">
         <v>94</v>
       </c>
       <c r="B8" t="s">
@@ -23599,7 +23584,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="35" t="s">
+      <c r="A13" t="s">
         <v>108</v>
       </c>
       <c r="B13" t="s">
@@ -23616,7 +23601,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="37" t="s">
+      <c r="A14" t="s">
         <v>98</v>
       </c>
       <c r="B14" t="s">
@@ -23633,7 +23618,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="37" t="s">
+      <c r="A15" t="s">
         <v>98</v>
       </c>
       <c r="B15" t="s">
@@ -23650,7 +23635,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="37" t="s">
+      <c r="A16" t="s">
         <v>98</v>
       </c>
       <c r="B16" t="s">
@@ -23667,7 +23652,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="37" t="s">
+      <c r="A17" t="s">
         <v>98</v>
       </c>
       <c r="B17" t="s">
@@ -23684,7 +23669,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="37" t="s">
+      <c r="A18" t="s">
         <v>98</v>
       </c>
       <c r="B18" t="s">
@@ -23701,7 +23686,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="37" t="s">
+      <c r="A19" t="s">
         <v>98</v>
       </c>
       <c r="B19" t="s">

--- a/public/data/Base_CeNtro Partner.xlsx
+++ b/public/data/Base_CeNtro Partner.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CeNtro Partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CC6F9DC-8B16-4D1D-87D9-9E777AA75190}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D24C976-44AE-490E-8ECE-8683B7AEFF9F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
   </bookViews>
   <sheets>
     <sheet name="Vista Sugerida" sheetId="37" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="149">
   <si>
     <t>Operaciones</t>
   </si>
@@ -482,6 +482,36 @@
   <si>
     <t>Gestion</t>
   </si>
+  <si>
+    <t>Logica YTD</t>
+  </si>
+  <si>
+    <t>Contar aquellos datos 1 o 0  , DATOS QUE APLIQUEN SE TOTALIZA</t>
+  </si>
+  <si>
+    <t>Ultimo dato del Mes que se tenga informacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contar aquellos datos 1 o 0  , DATOS QUE APLIQUEN SE TOTALIZA PERO SE DIVIDE EN EL TOTAL DE MESES 
+Ejemplo 18 Indicadores por Mes 
+YTD 108 Indicadores POSIBLES , se hace en aquellos que apliquen los blancos no se cuentan
+</t>
+  </si>
+  <si>
+    <t>Dato Columna YTD</t>
+  </si>
+  <si>
+    <t>Logica Selección Mes Multiple</t>
+  </si>
+  <si>
+    <t>Toma el Valor del mes mas cercano</t>
+  </si>
+  <si>
+    <t>Suma los Valores / la ponderacion es en el # Indicadores en rango / Indicadores Posibles</t>
+  </si>
+  <si>
+    <t>Promedia los Meses de Selección</t>
+  </si>
 </sst>
 </file>
 
@@ -677,7 +707,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -753,17 +783,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2752,17 +2785,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:E19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
-  <autoFilter ref="A1:E19" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E19">
-    <sortCondition ref="A2:A19" customList="Partner,Cliente,Negocio"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:G19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
+  <autoFilter ref="A1:G19" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G13">
+    <sortCondition ref="C2:C19" customList="NPS,Conexion,Desempeño,Bebida,SR%"/>
   </sortState>
-  <tableColumns count="5">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1DE9B01E-014D-4C21-9039-E85FAC7E9826}" name="Pilar"/>
     <tableColumn id="2" xr3:uid="{370F4551-C96B-4798-B9C2-B0D0DF6F0C9B}" name="Pestaña"/>
     <tableColumn id="3" xr3:uid="{DEE9CB88-C6EE-4808-946F-44FABBD87730}" name="Indicador"/>
     <tableColumn id="4" xr3:uid="{57EF6CB6-188F-4B83-A40F-EAEA47AE602F}" name="Ponderacion"/>
     <tableColumn id="5" xr3:uid="{6E373A24-B94B-4778-AB22-3DDCE2AF53B2}" name="Instrucción Comentario"/>
+    <tableColumn id="7" xr3:uid="{572EB68C-7535-4240-A7EC-DD33F512EEC0}" name="Logica Selección Mes Multiple"/>
+    <tableColumn id="6" xr3:uid="{4F7A2519-7D97-4DDE-A66E-B2FE23B6AF83}" name="Logica YTD"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3394,208 +3429,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="29" customHeight="1">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33" t="s">
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33" t="s">
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33" t="s">
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="33"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="35" t="s">
+      <c r="K2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="L2" s="35" t="s">
+      <c r="L2" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="M2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="P2" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="R2" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="S2" s="35" t="s">
+      <c r="S2" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="T2" s="35" t="s">
+      <c r="T2" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="U2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="V2" s="33"/>
+      <c r="V2" s="36"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="35">
-        <v>1</v>
-      </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="37">
+      <c r="C3" s="33">
+        <v>1</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="35">
         <v>0.88</v>
       </c>
     </row>
     <row r="4" spans="2:22">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="33">
         <v>2</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>3</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>4</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -19792,7 +19827,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" hidden="1">
       <c r="A2" s="26">
         <v>38115</v>
       </c>
@@ -19805,7 +19840,7 @@
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" hidden="1">
       <c r="A3" s="26">
         <v>38117</v>
       </c>
@@ -19816,7 +19851,7 @@
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" hidden="1">
       <c r="A4" s="26">
         <v>38119</v>
       </c>
@@ -19829,7 +19864,7 @@
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" hidden="1">
       <c r="A5" s="26">
         <v>38136</v>
       </c>
@@ -19842,7 +19877,7 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" hidden="1">
       <c r="A6" s="26">
         <v>38142</v>
       </c>
@@ -19855,7 +19890,7 @@
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" hidden="1">
       <c r="A7" s="26">
         <v>38149</v>
       </c>
@@ -19868,7 +19903,7 @@
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1">
       <c r="A8" s="26">
         <v>38176</v>
       </c>
@@ -19881,7 +19916,7 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="26">
         <v>38186</v>
       </c>
@@ -19894,7 +19929,7 @@
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1">
       <c r="A10" s="26">
         <v>38197</v>
       </c>
@@ -23401,17 +23436,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFDDE5B-0843-423B-B199-E3D9F7205F03}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53" customWidth="1"/>
+    <col min="6" max="6" width="73.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="87.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="16" t="s">
         <v>93</v>
       </c>
@@ -23427,8 +23464,14 @@
       <c r="E1" s="17" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="32" t="s">
         <v>94</v>
       </c>
@@ -23444,8 +23487,14 @@
       <c r="E2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="32" t="s">
         <v>94</v>
       </c>
@@ -23461,8 +23510,14 @@
       <c r="E3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="32" t="s">
         <v>94</v>
       </c>
@@ -23478,8 +23533,14 @@
       <c r="E4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="32" t="s">
         <v>94</v>
       </c>
@@ -23495,8 +23556,14 @@
       <c r="E5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="58">
       <c r="A6" s="32" t="s">
         <v>94</v>
       </c>
@@ -23512,8 +23579,14 @@
       <c r="E6" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="58">
       <c r="A7" s="32" t="s">
         <v>94</v>
       </c>
@@ -23529,8 +23602,14 @@
       <c r="E7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="58">
       <c r="A8" s="30" t="s">
         <v>94</v>
       </c>
@@ -23546,8 +23625,14 @@
       <c r="E8" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="30" t="s">
         <v>108</v>
       </c>
@@ -23563,16 +23648,22 @@
       <c r="E9" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="30" t="s">
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -23580,16 +23671,22 @@
       <c r="E10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="30" t="s">
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>132</v>
@@ -23597,8 +23694,14 @@
       <c r="E11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="30" t="s">
         <v>108</v>
       </c>
@@ -23614,8 +23717,14 @@
       <c r="E12" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>108</v>
       </c>
@@ -23631,8 +23740,14 @@
       <c r="E13" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -23648,8 +23763,14 @@
       <c r="E14" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -23665,8 +23786,14 @@
       <c r="E15" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -23682,8 +23809,14 @@
       <c r="E16" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -23699,8 +23832,14 @@
       <c r="E17" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -23716,8 +23855,14 @@
       <c r="E18" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -23732,6 +23877,12 @@
       </c>
       <c r="E19" t="s">
         <v>126</v>
+      </c>
+      <c r="F19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Base_CeNtro Partner.xlsx
+++ b/public/data/Base_CeNtro Partner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CeNtro Partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D24C976-44AE-490E-8ECE-8683B7AEFF9F}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16154FE6-BE1F-4C46-8582-486B7F438BD6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
   </bookViews>
@@ -29,12 +29,13 @@
     <sheet name="SR% " sheetId="22" r:id="rId14"/>
     <sheet name="Rotacion" sheetId="23" r:id="rId15"/>
     <sheet name="Bajas&lt;90" sheetId="26" r:id="rId16"/>
-    <sheet name="Estabilidad 12M" sheetId="27" r:id="rId17"/>
-    <sheet name="Estabilidad 24M" sheetId="30" r:id="rId18"/>
-    <sheet name="BB" sheetId="32" r:id="rId19"/>
-    <sheet name="BT" sheetId="33" r:id="rId20"/>
-    <sheet name="SS" sheetId="34" r:id="rId21"/>
-    <sheet name="Hoja3" sheetId="3" state="hidden" r:id="rId22"/>
+    <sheet name="Bajas" sheetId="38" r:id="rId17"/>
+    <sheet name="Estabilidad 12M" sheetId="27" r:id="rId18"/>
+    <sheet name="Estabilidad 24M" sheetId="30" r:id="rId19"/>
+    <sheet name="BB" sheetId="32" r:id="rId20"/>
+    <sheet name="BT" sheetId="33" r:id="rId21"/>
+    <sheet name="SS" sheetId="34" r:id="rId22"/>
+    <sheet name="Hoja3" sheetId="3" state="hidden" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="152">
   <si>
     <t>Operaciones</t>
   </si>
@@ -512,6 +513,15 @@
   <si>
     <t>Promedia los Meses de Selección</t>
   </si>
+  <si>
+    <t>Bajas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajas </t>
+  </si>
+  <si>
+    <t>&lt;= 1 = 1,  &gt;1 =0</t>
+  </si>
 </sst>
 </file>
 
@@ -788,14 +798,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2785,8 +2795,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:G19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
-  <autoFilter ref="A1:G19" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:G20" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
+  <autoFilter ref="A1:G20" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G13">
     <sortCondition ref="C2:C19" customList="NPS,Conexion,Desempeño,Bebida,SR%"/>
   </sortState>
@@ -2883,6 +2893,22 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{729C596F-9367-430B-AAB6-364A1ADD4E09}" name="Bajas" displayName="Bajas" ref="A1:G73" totalsRowShown="0">
+  <autoFilter ref="A1:G73" xr:uid="{729C596F-9367-430B-AAB6-364A1ADD4E09}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{46C8F9FA-CE10-4935-B9B9-7EFB267421FB}" name="CeCo"/>
+    <tableColumn id="2" xr3:uid="{49A6A0D0-DF94-4AB7-92A4-8E59B540BF04}" name="ene"/>
+    <tableColumn id="3" xr3:uid="{1910E027-20AE-4E42-A2DE-1D1760EEB0AB}" name="feb"/>
+    <tableColumn id="4" xr3:uid="{BAB40D7F-1CDB-45F4-9B83-1871D9BFE95D}" name="mar"/>
+    <tableColumn id="5" xr3:uid="{DBE908BB-1767-4CCC-B274-CEB1453A878D}" name="abr"/>
+    <tableColumn id="6" xr3:uid="{FEF46F54-81C9-4C87-BC3D-07DB0D2CCB0B}" name="may"/>
+    <tableColumn id="7" xr3:uid="{77EAB93B-7E9E-4961-B917-E5C100E70A63}" name="jun"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}" name="Estabilidad12M" displayName="Estabilidad12M" ref="A1:G73" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
@@ -2898,7 +2924,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7B08D3E-9BCB-4339-A04A-AD050E056D06}" name="Estabilidad12M18" displayName="Estabilidad12M18" ref="A1:G73" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:G73" xr:uid="{C2FD6B19-584A-460C-A035-77015EA4AB7A}"/>
   <tableColumns count="7">
@@ -2914,7 +2940,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}" name="Barista" displayName="Barista" ref="A1:G73" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:G73" xr:uid="{B5A8123F-4602-42B6-83C9-0E8474B2CADF}"/>
   <tableColumns count="7">
@@ -2930,7 +2956,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}" name="Supervisor" displayName="Supervisor" ref="A1:G73" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:G73" xr:uid="{CE1C3205-D3BA-41E4-A414-E8B5D13AFD3D}"/>
   <tableColumns count="7">
@@ -2941,22 +2967,6 @@
     <tableColumn id="5" xr3:uid="{858F5C44-74CD-4DDC-B14A-C3C05D1A1230}" name="abr" dataDxfId="18"/>
     <tableColumn id="6" xr3:uid="{FBE60864-83AB-4532-8B8A-0DE740421BF5}" name="may" dataDxfId="17"/>
     <tableColumn id="7" xr3:uid="{242FC6BB-64AE-4764-AFEB-2281526B13C4}" name="jun" dataDxfId="16"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:G73" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2974,6 +2984,22 @@
     <tableColumn id="6" xr3:uid="{8770BDB9-73F6-4F19-BB3C-E7766C80728D}" name="may"/>
     <tableColumn id="7" xr3:uid="{FD9D0AD6-87A5-4B92-843B-59D01D888BCA}" name="jun"/>
     <tableColumn id="9" xr3:uid="{BC77EBCD-2F33-4FA7-AABE-256E56761391}" name="YTD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}" name="Supervisor22" displayName="Supervisor22" ref="A1:G73" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:G73" xr:uid="{8DE080FC-3BED-4B80-BD7B-7F141035C834}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1A6BE1BB-6BD3-4BAD-9325-F832C6D568A7}" name="CeCo" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E10BDBC8-E28F-48B7-9653-0911E6C8F18B}" name="ene" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{74E1D7C4-BDDA-4A79-94C9-37C80D43D17A}" name="feb" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2CB75A52-99BA-4EC4-AAE8-D917C9AB908D}" name="mar" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7C4B692F-726D-4DFC-95D3-3D55878B9980}" name="abr" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D16EA3EA-919D-4EBD-98E7-A29DE29F07AC}" name="may" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{43402922-4FFB-465E-B4BE-823EAF456093}" name="jun" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3429,43 +3455,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="29" customHeight="1">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36" t="s">
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36" t="s">
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36" t="s">
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="2:22">
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="33" t="s">
         <v>109</v>
       </c>
@@ -3520,7 +3546,7 @@
       <c r="U2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="V2" s="36"/>
+      <c r="V2" s="37"/>
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="34" t="s">
@@ -16551,6 +16577,1706 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BABFBED-F34E-4FDE-B6D2-8D832ABA043A}">
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>38115</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>38117</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>38119</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>38136</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>38142</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>38149</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>38176</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>38186</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>38197</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>38205</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>38207</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>38230</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>38266</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>38270</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>38333</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>38339</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>38363</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>38368</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>38371</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>38374</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>38394</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>38401</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>38411</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>38427</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>38431</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>38442</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>38456</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>38458</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>38460</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>38475</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>38507</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>38515</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>38527</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>38529</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>38535</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>38546</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>38561</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>38590</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>38604</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>38606</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>38651</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>38656</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>38661</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>38674</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>38677</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>38694</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>38695</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>38719</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>38770</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>38792</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>38811</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>38837</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>38845</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>38859</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>38862</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>38894</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>38903</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>38924</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>38925</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>38930</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>38937</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>38965</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>38992</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>38995</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>43043</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>43111</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>43130</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>43132</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>43152</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>43193</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>43194</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>43195</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5390EF1C-3F04-4FB0-A927-950FD977A054}">
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -18191,7 +19917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FB737C-FC50-4021-B273-1837CB634325}">
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -19786,980 +21512,6 @@
       <c r="E73" s="28"/>
       <c r="F73" s="28"/>
       <c r="G73" s="28"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174F7617-EED9-47AF-8363-92A85480FF49}">
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="5.6328125" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1">
-      <c r="A2" s="26">
-        <v>38115</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26">
-        <v>1</v>
-      </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="1:7" hidden="1">
-      <c r="A3" s="26">
-        <v>38117</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-    </row>
-    <row r="4" spans="1:7" hidden="1">
-      <c r="A4" s="26">
-        <v>38119</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26">
-        <v>1</v>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-    </row>
-    <row r="5" spans="1:7" hidden="1">
-      <c r="A5" s="26">
-        <v>38136</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-    </row>
-    <row r="6" spans="1:7" hidden="1">
-      <c r="A6" s="26">
-        <v>38142</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26">
-        <v>1</v>
-      </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="1:7" hidden="1">
-      <c r="A7" s="26">
-        <v>38149</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26">
-        <v>1</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-    </row>
-    <row r="8" spans="1:7" hidden="1">
-      <c r="A8" s="26">
-        <v>38176</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-    </row>
-    <row r="9" spans="1:7" hidden="1">
-      <c r="A9" s="26">
-        <v>38186</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26">
-        <v>1</v>
-      </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-    </row>
-    <row r="10" spans="1:7" hidden="1">
-      <c r="A10" s="26">
-        <v>38197</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26">
-        <v>1</v>
-      </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="26">
-        <v>38205</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26">
-        <v>1</v>
-      </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26">
-        <v>1</v>
-      </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="26">
-        <v>38207</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26">
-        <v>1</v>
-      </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26">
-        <v>0</v>
-      </c>
-      <c r="G12" s="26"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="26">
-        <v>38230</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="26">
-        <v>38266</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26">
-        <v>1</v>
-      </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="26">
-        <v>38270</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26">
-        <v>1</v>
-      </c>
-      <c r="E15" s="26">
-        <v>1</v>
-      </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="26">
-        <v>38333</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26">
-        <v>1</v>
-      </c>
-      <c r="F16" s="26">
-        <v>0</v>
-      </c>
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="26">
-        <v>38339</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26">
-        <v>1</v>
-      </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26">
-        <v>1</v>
-      </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="26">
-        <v>38363</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26">
-        <v>1</v>
-      </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26">
-        <v>1</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="26">
-        <v>38368</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26">
-        <v>1</v>
-      </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="26">
-        <v>38371</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26">
-        <v>1</v>
-      </c>
-      <c r="E20" s="26">
-        <v>1</v>
-      </c>
-      <c r="F20" s="26">
-        <v>1</v>
-      </c>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="26">
-        <v>38374</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26">
-        <v>1</v>
-      </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="26">
-        <v>38394</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26">
-        <v>1</v>
-      </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="26">
-        <v>38401</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="26">
-        <v>38411</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26">
-        <v>1</v>
-      </c>
-      <c r="D24" s="26">
-        <v>1</v>
-      </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="26">
-        <v>38427</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="26">
-        <v>38431</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26">
-        <v>0</v>
-      </c>
-      <c r="E26" s="26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="26">
-        <v>38442</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="26">
-        <v>38456</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26">
-        <v>1</v>
-      </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26">
-        <v>1</v>
-      </c>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="26">
-        <v>38458</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26">
-        <v>1</v>
-      </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="26">
-        <v>38460</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26">
-        <v>1</v>
-      </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26">
-        <v>1</v>
-      </c>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="26">
-        <v>38475</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26">
-        <v>0</v>
-      </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="26">
-        <v>38507</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="26">
-        <v>38515</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26">
-        <v>1</v>
-      </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="26">
-        <v>38527</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26">
-        <v>1</v>
-      </c>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="26">
-        <v>38529</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26">
-        <v>1</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1</v>
-      </c>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="26">
-        <v>38535</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26">
-        <v>1</v>
-      </c>
-      <c r="D36" s="26">
-        <v>1</v>
-      </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26">
-        <v>0</v>
-      </c>
-      <c r="G36" s="26"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="26">
-        <v>38546</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26">
-        <v>1</v>
-      </c>
-      <c r="E37" s="26">
-        <v>1</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1</v>
-      </c>
-      <c r="G37" s="26"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="26">
-        <v>38561</v>
-      </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26">
-        <v>1</v>
-      </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="26">
-        <v>38590</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="26">
-        <v>38604</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26">
-        <v>1</v>
-      </c>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="26">
-        <v>38606</v>
-      </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="26">
-        <v>38651</v>
-      </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26">
-        <v>1</v>
-      </c>
-      <c r="G42" s="26"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="26">
-        <v>38656</v>
-      </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="26">
-        <v>38661</v>
-      </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26">
-        <v>1</v>
-      </c>
-      <c r="G44" s="26"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="26">
-        <v>38674</v>
-      </c>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26">
-        <v>1</v>
-      </c>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="26">
-        <v>38677</v>
-      </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26">
-        <v>1</v>
-      </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="26">
-        <v>38694</v>
-      </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="26">
-        <v>38695</v>
-      </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26">
-        <v>1</v>
-      </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="26">
-        <v>38719</v>
-      </c>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26">
-        <v>1</v>
-      </c>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="26">
-        <v>38770</v>
-      </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="26">
-        <v>38792</v>
-      </c>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="26">
-        <v>38811</v>
-      </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26">
-        <v>1</v>
-      </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="26">
-        <v>38837</v>
-      </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26">
-        <v>1</v>
-      </c>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="26">
-        <v>38845</v>
-      </c>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26">
-        <v>1</v>
-      </c>
-      <c r="F54" s="26">
-        <v>1</v>
-      </c>
-      <c r="G54" s="26"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="26">
-        <v>38859</v>
-      </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26">
-        <v>1</v>
-      </c>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="26">
-        <v>38862</v>
-      </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26">
-        <v>1</v>
-      </c>
-      <c r="E56" s="26">
-        <v>1</v>
-      </c>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="26">
-        <v>38894</v>
-      </c>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="26">
-        <v>38903</v>
-      </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="26">
-        <v>38924</v>
-      </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="26">
-        <v>38925</v>
-      </c>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="26">
-        <v>38930</v>
-      </c>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="26">
-        <v>38937</v>
-      </c>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="26">
-        <v>38965</v>
-      </c>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26">
-        <v>1</v>
-      </c>
-      <c r="E63" s="26">
-        <v>1</v>
-      </c>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="26">
-        <v>38992</v>
-      </c>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26">
-        <v>1</v>
-      </c>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="26">
-        <v>38995</v>
-      </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26">
-        <v>1</v>
-      </c>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="26">
-        <v>43043</v>
-      </c>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26">
-        <v>1</v>
-      </c>
-      <c r="D66" s="26">
-        <v>1</v>
-      </c>
-      <c r="E66" s="26">
-        <v>1</v>
-      </c>
-      <c r="F66" s="26">
-        <v>0</v>
-      </c>
-      <c r="G66" s="26"/>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="26">
-        <v>43111</v>
-      </c>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="26">
-        <v>43130</v>
-      </c>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="26">
-        <v>43132</v>
-      </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="26">
-        <v>43152</v>
-      </c>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26">
-        <v>1</v>
-      </c>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="26">
-        <v>43193</v>
-      </c>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="26">
-        <v>43194</v>
-      </c>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="26">
-        <v>43195</v>
-      </c>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21600,6 +22352,980 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174F7617-EED9-47AF-8363-92A85480FF49}">
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="5.6328125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1">
+      <c r="A2" s="26">
+        <v>38115</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" hidden="1">
+      <c r="A3" s="26">
+        <v>38117</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" hidden="1">
+      <c r="A4" s="26">
+        <v>38119</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
+      <c r="A5" s="26">
+        <v>38136</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26">
+        <v>1</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="1:7" hidden="1">
+      <c r="A6" s="26">
+        <v>38142</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26">
+        <v>1</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" hidden="1">
+      <c r="A7" s="26">
+        <v>38149</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26">
+        <v>1</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
+      <c r="A8" s="26">
+        <v>38176</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
+      <c r="A9" s="26">
+        <v>38186</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26">
+        <v>1</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" hidden="1">
+      <c r="A10" s="26">
+        <v>38197</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26">
+        <v>1</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="26">
+        <v>38205</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26">
+        <v>1</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26">
+        <v>1</v>
+      </c>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="26">
+        <v>38207</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26">
+        <v>1</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="26">
+        <v>38230</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="26">
+        <v>38266</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26">
+        <v>1</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="26">
+        <v>38270</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26">
+        <v>1</v>
+      </c>
+      <c r="E15" s="26">
+        <v>1</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="26">
+        <v>38333</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26">
+        <v>1</v>
+      </c>
+      <c r="F16" s="26">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="26">
+        <v>38339</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26">
+        <v>1</v>
+      </c>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26">
+        <v>1</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="26">
+        <v>38363</v>
+      </c>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26">
+        <v>1</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26">
+        <v>1</v>
+      </c>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="26">
+        <v>38368</v>
+      </c>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26">
+        <v>1</v>
+      </c>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="26">
+        <v>38371</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26">
+        <v>1</v>
+      </c>
+      <c r="E20" s="26">
+        <v>1</v>
+      </c>
+      <c r="F20" s="26">
+        <v>1</v>
+      </c>
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="26">
+        <v>38374</v>
+      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26">
+        <v>1</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="26">
+        <v>38394</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26">
+        <v>1</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="26">
+        <v>38401</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="26">
+        <v>38411</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26">
+        <v>1</v>
+      </c>
+      <c r="D24" s="26">
+        <v>1</v>
+      </c>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="26">
+        <v>38427</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="26">
+        <v>38431</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="26">
+        <v>38442</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="26">
+        <v>38456</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26">
+        <v>1</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26">
+        <v>1</v>
+      </c>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="26">
+        <v>38458</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26">
+        <v>1</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="26">
+        <v>38460</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26">
+        <v>1</v>
+      </c>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="26">
+        <v>38475</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26">
+        <v>0</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="26">
+        <v>38507</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="26">
+        <v>38515</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26">
+        <v>1</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="26">
+        <v>38527</v>
+      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26">
+        <v>1</v>
+      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="26">
+        <v>38529</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26">
+        <v>1</v>
+      </c>
+      <c r="E35" s="26">
+        <v>1</v>
+      </c>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="26">
+        <v>38535</v>
+      </c>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26">
+        <v>1</v>
+      </c>
+      <c r="D36" s="26">
+        <v>1</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26">
+        <v>0</v>
+      </c>
+      <c r="G36" s="26"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="26">
+        <v>38546</v>
+      </c>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26">
+        <v>1</v>
+      </c>
+      <c r="E37" s="26">
+        <v>1</v>
+      </c>
+      <c r="F37" s="26">
+        <v>1</v>
+      </c>
+      <c r="G37" s="26"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="26">
+        <v>38561</v>
+      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26">
+        <v>1</v>
+      </c>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="26">
+        <v>38590</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="26">
+        <v>38604</v>
+      </c>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26">
+        <v>1</v>
+      </c>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="26">
+        <v>38606</v>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="26">
+        <v>38651</v>
+      </c>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26">
+        <v>1</v>
+      </c>
+      <c r="G42" s="26"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="26">
+        <v>38656</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="26">
+        <v>38661</v>
+      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26">
+        <v>1</v>
+      </c>
+      <c r="G44" s="26"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="26">
+        <v>38674</v>
+      </c>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26">
+        <v>1</v>
+      </c>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="26">
+        <v>38677</v>
+      </c>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26">
+        <v>1</v>
+      </c>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="26">
+        <v>38694</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="26">
+        <v>38695</v>
+      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26">
+        <v>1</v>
+      </c>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="26">
+        <v>38719</v>
+      </c>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26">
+        <v>1</v>
+      </c>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="26">
+        <v>38770</v>
+      </c>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="26">
+        <v>38792</v>
+      </c>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="26">
+        <v>38811</v>
+      </c>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26">
+        <v>1</v>
+      </c>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="26">
+        <v>38837</v>
+      </c>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26">
+        <v>1</v>
+      </c>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="26">
+        <v>38845</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26">
+        <v>1</v>
+      </c>
+      <c r="F54" s="26">
+        <v>1</v>
+      </c>
+      <c r="G54" s="26"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="26">
+        <v>38859</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26">
+        <v>1</v>
+      </c>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="26">
+        <v>38862</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26">
+        <v>1</v>
+      </c>
+      <c r="E56" s="26">
+        <v>1</v>
+      </c>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="26">
+        <v>38894</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="26">
+        <v>38903</v>
+      </c>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="26">
+        <v>38924</v>
+      </c>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="26">
+        <v>38925</v>
+      </c>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="26">
+        <v>38930</v>
+      </c>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="26">
+        <v>38937</v>
+      </c>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="26">
+        <v>38965</v>
+      </c>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26">
+        <v>1</v>
+      </c>
+      <c r="E63" s="26">
+        <v>1</v>
+      </c>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="26">
+        <v>38992</v>
+      </c>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26">
+        <v>1</v>
+      </c>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="26">
+        <v>38995</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26">
+        <v>1</v>
+      </c>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="26">
+        <v>43043</v>
+      </c>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26">
+        <v>1</v>
+      </c>
+      <c r="D66" s="26">
+        <v>1</v>
+      </c>
+      <c r="E66" s="26">
+        <v>1</v>
+      </c>
+      <c r="F66" s="26">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="26">
+        <v>43111</v>
+      </c>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="26">
+        <v>43130</v>
+      </c>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="26">
+        <v>43132</v>
+      </c>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="26">
+        <v>43152</v>
+      </c>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26">
+        <v>1</v>
+      </c>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="26">
+        <v>43193</v>
+      </c>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="26">
+        <v>43194</v>
+      </c>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="26">
+        <v>43195</v>
+      </c>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC789C37-048E-4AE0-8E70-A8B9675D4E16}">
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -22517,7 +24243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB6110A-93E3-4BF4-BE40-9390D9D04E18}">
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
@@ -23402,7 +25128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B490CD3-F038-4249-AC87-7B4BF285EC1F}">
   <sheetPr codeName="Hoja12"/>
   <dimension ref="A1:B3"/>
@@ -23436,7 +25162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFDDE5B-0843-423B-B199-E3D9F7205F03}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -23582,7 +25308,7 @@
       <c r="F6" t="s">
         <v>147</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="36" t="s">
         <v>143</v>
       </c>
     </row>
@@ -23605,7 +25331,7 @@
       <c r="F7" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="36" t="s">
         <v>143</v>
       </c>
     </row>
@@ -23628,7 +25354,7 @@
       <c r="F8" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="36" t="s">
         <v>143</v>
       </c>
     </row>
@@ -23883,6 +25609,29 @@
       </c>
       <c r="G19" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Base_CeNtro Partner.xlsx
+++ b/public/data/Base_CeNtro Partner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CeNtro Partner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16154FE6-BE1F-4C46-8582-486B7F438BD6}"/>
+  <xr:revisionPtr revIDLastSave="580" documentId="13_ncr:1_{760AD2FD-697A-4E92-8D4F-188A5F96FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB503E6-A921-421B-952C-03A7050E8A86}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{38B5B763-1661-4426-8397-08C7B1466D39}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="155">
   <si>
     <t>Operaciones</t>
   </si>
@@ -522,6 +522,15 @@
   <si>
     <t>&lt;= 1 = 1,  &gt;1 =0</t>
   </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Ops ,RH</t>
+  </si>
+  <si>
+    <t>Ops</t>
+  </si>
 </sst>
 </file>
 
@@ -717,7 +726,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -807,6 +816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2795,13 +2805,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:G20" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
-  <autoFilter ref="A1:G20" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G13">
-    <sortCondition ref="C2:C19" customList="NPS,Conexion,Desempeño,Bebida,SR%"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}" name="instrucciones" displayName="instrucciones" ref="A1:H20" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
+  <autoFilter ref="A1:H20" xr:uid="{397D8347-75D2-4809-AF53-3D9C7B8DBEBD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:H13">
+    <sortCondition ref="D2:D19" customList="NPS,Conexion,Desempeño,Bebida,SR%"/>
   </sortState>
-  <tableColumns count="7">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{1DE9B01E-014D-4C21-9039-E85FAC7E9826}" name="Pilar"/>
+    <tableColumn id="8" xr3:uid="{EA572C8B-0BC0-444E-908C-F7F076860675}" name="Area"/>
     <tableColumn id="2" xr3:uid="{370F4551-C96B-4798-B9C2-B0D0DF6F0C9B}" name="Pestaña"/>
     <tableColumn id="3" xr3:uid="{DEE9CB88-C6EE-4808-946F-44FABBD87730}" name="Indicador"/>
     <tableColumn id="4" xr3:uid="{57EF6CB6-188F-4B83-A40F-EAEA47AE602F}" name="Ponderacion"/>
@@ -25162,475 +25173,535 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFFDDE5B-0843-423B-B199-E3D9F7205F03}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="73.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="87.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53" customWidth="1"/>
+    <col min="7" max="7" width="73.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="87.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="16" t="s">
         <v>93</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B2" t="s">
-        <v>109</v>
+      <c r="B2" s="39" t="s">
+        <v>153</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
         <v>134</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>126</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>146</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B3" t="s">
-        <v>110</v>
+      <c r="B3" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>110</v>
       </c>
       <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>126</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>147</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B4" t="s">
-        <v>111</v>
+      <c r="B4" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>111</v>
       </c>
       <c r="D4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" t="s">
         <v>136</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>126</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>146</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B5" t="s">
-        <v>112</v>
+      <c r="B5" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>112</v>
       </c>
       <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" t="s">
         <v>136</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>126</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>146</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="58">
+    <row r="6" spans="1:8" ht="58">
       <c r="A6" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B6" t="s">
-        <v>113</v>
+      <c r="B6" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>113</v>
       </c>
       <c r="D6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" t="s">
         <v>137</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>126</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>147</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="H6" s="36" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58">
+    <row r="7" spans="1:8" ht="58">
       <c r="A7" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B7" t="s">
-        <v>114</v>
+      <c r="B7" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>114</v>
       </c>
       <c r="D7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" t="s">
         <v>137</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>126</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="H7" s="36" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58">
+    <row r="8" spans="1:8" ht="58">
       <c r="A8" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B8" t="s">
-        <v>115</v>
+      <c r="B8" s="39" t="s">
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
       </c>
       <c r="D8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" t="s">
         <v>137</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>126</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="H8" s="36" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
-        <v>103</v>
+      <c r="B9" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
       </c>
       <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
         <v>130</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>126</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>148</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B10" t="s">
-        <v>104</v>
+      <c r="B10" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
       </c>
       <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
         <v>131</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>126</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>148</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B11" t="s">
-        <v>105</v>
+      <c r="B11" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="C11" t="s">
         <v>105</v>
       </c>
       <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
         <v>132</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>126</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>148</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B12" t="s">
-        <v>106</v>
+      <c r="B12" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="C12" t="s">
         <v>106</v>
       </c>
       <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
         <v>132</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>126</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>148</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
         <v>107</v>
       </c>
       <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
         <v>133</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>126</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>148</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>98</v>
       </c>
       <c r="B14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" t="s">
         <v>96</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>117</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>124</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>126</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>148</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>98</v>
       </c>
       <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>118</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>127</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>126</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>148</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>98</v>
       </c>
       <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
         <v>99</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>119</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>127</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>126</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>148</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>98</v>
       </c>
       <c r="B17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" t="s">
         <v>100</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>120</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>127</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>126</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>148</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>98</v>
       </c>
       <c r="B18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" t="s">
         <v>101</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E18" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>126</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>148</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>98</v>
       </c>
       <c r="B19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" t="s">
         <v>102</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>122</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>129</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>126</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>148</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>94</v>
       </c>
       <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>149</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>150</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>151</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>126</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>147</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="H20" s="36" t="s">
         <v>141</v>
       </c>
     </row>
